--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260922.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,600,000</t>
+          <t>9,400,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.25%</t>
+          <t>14.74%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.16%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.12%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.96%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,830,000</t>
+          <t>2,900,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>645,000</t>
+          <t>646,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,987,956</t>
+          <t>2,060,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>1,867,956</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -902,73 +902,73 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>13,500,000</t>
+          <t>2,770,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>13,500,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,770,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>120,500</t>
+          <t>1,625,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,580,000</t>
+          <t>120,500</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>280,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>280,000</t>
+          <t>680,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1183,29 +1183,29 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1349,154 +1349,154 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>191,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>191,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1518,85 +1518,85 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,39 +1701,35 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>8,121,787,272</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>7,687,010,893</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1741,17 +1737,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,628,895,497</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1759,38 +1755,20 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RP_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>676,227,108</t>
+          <t>3,992,237,825</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>RP_NTD</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>3,992,237,825</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
